--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484689_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484689_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0604</v>
+        <v>4.2256</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6445</v>
+        <v>4.0769</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4158</v>
+        <v>0.1487</v>
       </c>
       <c r="G2" t="n">
-        <v>1.959</v>
+        <v>6.6209</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4515</v>
+        <v>-1.5536</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4104</v>
+        <v>8.1745</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5457</v>
+        <v>7.2669</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7179</v>
+        <v>-0.6194</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8278</v>
+        <v>7.8863</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5867</v>
+        <v>-0.646</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1694</v>
+        <v>-0.9342</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4173</v>
+        <v>0.2882</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.2828</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.5814</v>
+        <v>-2.7489</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2986</v>
+        <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1021</v>
+        <v>-0.8974</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1206</v>
+        <v>-0.4412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0186</v>
+        <v>-0.4563</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4863</v>
+        <v>-0.5816</v>
       </c>
       <c r="W2" t="n">
-        <v>3.8009</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6854</v>
+        <v>-0.5816</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5437</v>
+        <v>3.4055</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6923</v>
+        <v>1.6585</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1486</v>
+        <v>1.747</v>
       </c>
       <c r="G3" t="n">
-        <v>6.6209</v>
+        <v>1.959</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5536</v>
+        <v>-0.4515</v>
       </c>
       <c r="I3" t="n">
-        <v>8.1745</v>
+        <v>2.4104</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2669</v>
+        <v>3.5457</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6194</v>
+        <v>0.7179</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8863</v>
+        <v>2.8278</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.646</v>
+        <v>-1.5867</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9342</v>
+        <v>-1.1694</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2882</v>
+        <v>-0.4173</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9163</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7489</v>
+        <v>-4.5814</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>3.2986</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5793</v>
+        <v>-1.757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8258</v>
+        <v>-1.1067</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7536</v>
+        <v>-0.6503</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5816</v>
+        <v>4.4863</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.8009</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5816</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7481</v>
+        <v>1.6633</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1782</v>
+        <v>1.9448</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4302</v>
+        <v>-0.2815</v>
       </c>
       <c r="G4" t="n">
         <v>0.411</v>
@@ -766,13 +766,13 @@
         <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6965</v>
+        <v>-1.7813</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.405</v>
+        <v>-0.6384</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2916</v>
+        <v>-1.1429</v>
       </c>
       <c r="V4" t="n">
         <v>1.0177</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2274</v>
+        <v>1.5826</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2717</v>
+        <v>2.2306</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0444</v>
+        <v>-0.648</v>
       </c>
       <c r="G5" t="n">
         <v>0.2282</v>
@@ -844,13 +844,13 @@
         <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9348</v>
+        <v>-1.5796</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3499</v>
+        <v>-0.391</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.5849</v>
+        <v>-1.1886</v>
       </c>
       <c r="V5" t="n">
         <v>1.6512</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5524</v>
+        <v>0.8989</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1754</v>
+        <v>0.4227</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3771</v>
+        <v>0.4762</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9639</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0335</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6606</v>
+        <v>-0.4133</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3729</v>
+        <v>-0.2738</v>
       </c>
       <c r="V6" t="n">
         <v>1.267</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1432</v>
+        <v>-0.5743</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.2578</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4853</v>
+        <v>-0.8321</v>
       </c>
       <c r="G7" t="n">
         <v>0.4933</v>
@@ -1000,13 +1000,13 @@
         <v>3.1154</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0721</v>
+        <v>-1.7896</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4796</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5925</v>
+        <v>-0.9393</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5608</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0289</v>
+        <v>-1.9794</v>
       </c>
       <c r="E8" t="n">
         <v>-0.8179</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.211</v>
+        <v>-1.1615</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1351</v>
@@ -1078,13 +1078,13 @@
         <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4436</v>
+        <v>-0.394</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2234</v>
+        <v>-0.1738</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6335</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6165</v>
+        <v>-2.5177</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.472</v>
+        <v>-4.2246</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8555</v>
+        <v>1.7069</v>
       </c>
       <c r="G9" t="n">
         <v>1.7351</v>
@@ -1156,13 +1156,13 @@
         <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6368</v>
+        <v>-1.5381</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.046</v>
+        <v>-0.7986</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5908</v>
+        <v>-0.7395</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3324</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.416</v>
+        <v>-3.3391</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7124</v>
+        <v>-2.5612</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7036</v>
+        <v>-0.7779</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6684</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.177</v>
+        <v>-0.1001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4404</v>
+        <v>-0.2892</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2634</v>
+        <v>0.1891</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6543</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1145</v>
+        <v>-3.7155</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9657</v>
+        <v>-1.8145</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1488</v>
+        <v>-1.9011</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3995</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9532</v>
+        <v>-0.5543</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6056</v>
+        <v>-0.4544</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3477</v>
+        <v>-0.0999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.212</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9007000000000009</v>
+        <v>-0.3501000000000007</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6225999999999989</v>
+        <v>1.173100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.523500000000001</v>
+        <v>-1.5233</v>
       </c>
       <c r="G12" t="n">
         <v>7.280600000000002</v>
@@ -1390,13 +1390,13 @@
         <v>17.4095</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.6289</v>
+        <v>-11.0784</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.153700000000001</v>
+        <v>-5.6033</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.4754</v>
+        <v>-5.475300000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.4476</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4636</v>
+        <v>9.2921</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0468</v>
+        <v>6.4699</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4168</v>
+        <v>2.8222</v>
       </c>
       <c r="G13" t="n">
         <v>5.0999</v>
@@ -1468,13 +1468,13 @@
         <v>2.9321</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9286</v>
+        <v>2.7572</v>
       </c>
       <c r="T13" t="n">
-        <v>1.902</v>
+        <v>1.3251</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0266</v>
+        <v>1.4321</v>
       </c>
       <c r="V13" t="n">
         <v>0.702</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0198</v>
+        <v>3.7284</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3966</v>
+        <v>2.2043</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6232</v>
+        <v>1.5241</v>
       </c>
       <c r="G14" t="n">
         <v>1.2533</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0335</v>
+        <v>0.7421</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0166</v>
+        <v>-0.1757</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0169</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.6335</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8395</v>
+        <v>2.0436</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3702</v>
+        <v>1.1779</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4693</v>
+        <v>0.8657</v>
       </c>
       <c r="G15" t="n">
         <v>0.5504</v>
@@ -1624,13 +1624,13 @@
         <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5561</v>
+        <v>0.7602</v>
       </c>
       <c r="T15" t="n">
-        <v>0.31</v>
+        <v>0.1177</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2461</v>
+        <v>0.6425</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.403</v>
+        <v>1.8371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1834</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2196</v>
+        <v>1.2691</v>
       </c>
       <c r="G16" t="n">
         <v>0.1137</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6447</v>
+        <v>2.0788</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5098</v>
+        <v>0.8945</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1348</v>
+        <v>1.1844</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8215</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0338</v>
+        <v>-0.4044</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3003</v>
+        <v>0.1805</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7335</v>
+        <v>-0.5849</v>
       </c>
       <c r="G19" t="n">
         <v>-2.344</v>
@@ -1936,13 +1936,13 @@
         <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3783</v>
+        <v>0.2511</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6795</v>
+        <v>-0.1987</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3012</v>
+        <v>0.4498</v>
       </c>
       <c r="V19" t="n">
         <v>0.9554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5591</v>
+        <v>-0.4301</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0587</v>
+        <v>-0.9049</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4996</v>
+        <v>0.4748</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9254</v>
@@ -2014,13 +2014,13 @@
         <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4011</v>
+        <v>0.7279</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4223</v>
+        <v>0.7315</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0212</v>
+        <v>-0.0036</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2326</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5623</v>
+        <v>-1.1441</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2824</v>
+        <v>-4.1863</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7201</v>
+        <v>3.0422</v>
       </c>
       <c r="G21" t="n">
         <v>1.8888</v>
@@ -2092,13 +2092,13 @@
         <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.9248</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1123</v>
+        <v>-0.0162</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6189</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2088</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5392</v>
+        <v>-2.2974</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3561</v>
+        <v>-0.1638</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1831</v>
+        <v>-2.1336</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6086</v>
@@ -2170,13 +2170,13 @@
         <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3704</v>
+        <v>-0.1286</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2753</v>
+        <v>-0.083</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0456</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6439</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.954</v>
+        <v>-3.2118</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0653</v>
+        <v>-2.546</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8888</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-4.724</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>0.715</v>
+        <v>0.4572</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6946</v>
+        <v>0.2138</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0204</v>
+        <v>0.2434</v>
       </c>
       <c r="V23" t="n">
         <v>0.3219</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2131</v>
+        <v>-3.8587</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6928</v>
+        <v>-1.8502</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9058</v>
+        <v>-2.0086</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.5262</v>
+        <v>-4.9588</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0704</v>
+        <v>-1.378</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4558</v>
+        <v>-3.5808</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7876</v>
+        <v>-0.6676</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3133</v>
+        <v>-0.0683</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4743</v>
+        <v>-0.5994</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.7386</v>
+        <v>-4.2911</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7572</v>
+        <v>-1.3097</v>
       </c>
       <c r="O24" t="n">
         <v>-2.9815</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.1991</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5115</v>
+        <v>0.888</v>
       </c>
       <c r="T24" t="n">
-        <v>3.991</v>
+        <v>0.6946</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5206</v>
+        <v>0.1934</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.0989</v>
+        <v>0.945</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7873</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.864</v>
+        <v>-6.5544</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.004</v>
+        <v>-1.3265</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8599</v>
+        <v>-5.2279</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.9588</v>
+        <v>-4.5262</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.378</v>
+        <v>-1.0704</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.5808</v>
+        <v>-3.4558</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6676</v>
+        <v>-0.7876</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0683</v>
+        <v>-0.3133</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5994</v>
+        <v>-0.4743</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.2911</v>
+        <v>-3.7386</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3097</v>
+        <v>-0.7572</v>
       </c>
       <c r="O25" t="n">
         <v>-2.9815</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.1991</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1172</v>
+        <v>2.1703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4593</v>
+        <v>1.9717</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3421</v>
+        <v>0.1985</v>
       </c>
       <c r="V25" t="n">
-        <v>0.945</v>
+        <v>-3.0989</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X25" t="n">
-        <v>0.6231</v>
+        <v>-2.7873</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9007999999999985</v>
+        <v>0.9007000000000005</v>
       </c>
       <c r="E26" t="n">
-        <v>1.523399999999999</v>
+        <v>1.523299999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6227</v>
       </c>
       <c r="G26" t="n">
         <v>-7.2805</v>
@@ -2458,7 +2458,7 @@
         <v>9.261599999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>7.815899999999998</v>
+        <v>7.815899999999997</v>
       </c>
       <c r="L26" t="n">
         <v>1.4456</v>
@@ -2473,7 +2473,7 @@
         <v>-13.3054</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.0001000000000001</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.4095</v>
@@ -2488,7 +2488,7 @@
         <v>5.4753</v>
       </c>
       <c r="U26" t="n">
-        <v>6.153600000000001</v>
+        <v>6.1537</v>
       </c>
       <c r="V26" t="n">
         <v>-3.4479</v>
